--- a/build/fees-discounts/PO-Questions-Round2.xlsx
+++ b/build/fees-discounts/PO-Questions-Round2.xlsx
@@ -586,7 +586,12 @@
 B) Silent is fine - no warning needed, as long as the credited amount is exact (which it is today).</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>ANSWER: A (Chris Ward, 2026-07-14): "A - already resolved: the warning exists and is spec-required (S6-R12, 'the carry is never silent'). It shows before invoicing and before marking the WO reviewed/complete, stating the $0.00 floor, that tax on the taxable base is still owed, and the exact credit amount, and requires confirmation. It intentionally doesn't fire when the adjustment is merely added (nothing committed yet; the add dialog's preview shows the resulting totals). No change needed."
+RESULTING ACTION: Warning is required and (per PO) already exists at commit points. FDBUG-15 reclassified NOT-A-DEFECT (our add-time observation was the wrong trigger point); no dev ticket created. FD-QB-014 (C28557) expected reworded to the commit-point warning; status -&gt; VIU-Pending (needs a commit-time re-VIU). Staged for TestRail push (awaiting authorization).</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="150" customHeight="1">
       <c r="A6" s="4" t="n">
@@ -614,7 +619,12 @@
 C) Don't allow it - the app should refuse 0 in the maximum box and ask for a real amount (or an empty box).</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>ANSWER: A (Chris Ward, 2026-07-14): "A - already resolved by spec: S2-R25 says an entered 0 is treated the same as empty, i.e. no maximum. Working as designed; a true $0 cap can only come from legacy data (S5-R6 note), never from the UI. No change needed."
+RESULTING ACTION: 0 = 'no limit' is working as designed. FDBUG-9 closed as accepted; TICKET 4 DROPPED. FD-CALC-008 (C28575), FD-VAL-006 (C28604), FD-TMPL-011 (C28512) expecteds reworded to affirm 0 = no cap; all flipped to VIU-Verified. Staged for TestRail push (awaiting authorization).</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="150" customHeight="1">
       <c r="A7" s="4" t="n">
@@ -642,7 +652,12 @@
 C) Refuse it - the app should reject anything smaller than 0.01% with a clear message, so the user knowingly picks a valid value.</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>ANSWER: A (Chris Ward, 2026-07-14): "A -- fully anticipated and expected."
+RESULTING ACTION: Quietly rounding tiny percentages up to the 0.01% minimum is expected. FDBUG-10 closed as accepted; TICKET 5 DROPPED. FD-CALC-006 (C28573) expected reworded to expect the round-up-to-minimum coercion; flipped to VIU-Verified. Staged for TestRail push (awaiting authorization).</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="150" customHeight="1">
       <c r="A8" s="4" t="n">
@@ -669,7 +684,12 @@
 B) Don't support it - but make that clear: remove/disable the box for processing fees (or show a message) so nothing a user types is ever silently thrown away.</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>ANSWER: B (Chris Ward, 2026-07-14): "B - already resolved by spec: S8-N6 forbids a Processing Fee minimum. Premise doesn't reproduce: there is no minimum-amount field anywhere in the UI, and the API rejects a Processing Fee minimum with an explicit error ('A processing fee cannot have a minimum or maximum cap') - nothing is silently dropped. No change needed."
+RESULTING ACTION: Processing fees don't support a minimum and the app already makes that clear (no field + explicit API reject - matches the live 2026-07-13 finding). FD-PROC-014 (C28532) expected reworded to the explicit-reject + no-field behavior; stays VIU-Verified. No dev ticket. Staged for TestRail push (awaiting authorization).</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -773,7 +793,7 @@
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>FD-QB-014 = VIU-Deviation (FDBUG-15 CONFIRMED AGAIN 2026-07-10: over-discount saves 201 with no warning payload; batch-6 UI shots show no warn/confirm dialog). Currently bucketed case-update pending this PO ruling. A=defect ticket + keep spec expected; B=case-update FD-QB-014 to silent-carry expected.</t>
+          <t>FD-QB-014 = VIU-Deviation (FDBUG-15 CONFIRMED AGAIN 2026-07-10: over-discount saves 201 with no warning payload; batch-6 UI shots show no warn/confirm dialog). Currently bucketed case-update pending this PO ruling. A=defect ticket + keep spec expected; B=case-update FD-QB-014 to silent-carry expected. ANSWERED 2026-07-14 = A (warning exists at commit points; add-time silent is intentional). Applied: FDBUG-15 reclassified NOT-A-DEFECT (no ticket); FD-QB-014 expected reworded to the commit-point warning; status -&gt; VIU-Pending (commit-time re-VIU outstanding). Staged for TestRail push.</t>
         </is>
       </c>
     </row>
@@ -850,7 +870,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>FD-CALC-008 / FD-VAL-006 / FD-TMPL-011 = VIU-Deviation (FDBUG-9 CONFIRMED AGAIN 2026-07-10: maxCap 0 stored, 10% resolved 34.15 = uncapped). A=case-update all 3 to "0 = no cap" + drop TICKET 4; B=file TICKET 4 as drafted (§5-R6); C=new validation requirement + case updates.</t>
+          <t>FD-CALC-008 / FD-VAL-006 / FD-TMPL-011 = VIU-Deviation (FDBUG-9 CONFIRMED AGAIN 2026-07-10: maxCap 0 stored, 10% resolved 34.15 = uncapped). A=case-update all 3 to "0 = no cap" + drop TICKET 4; B=file TICKET 4 as drafted (§5-R6); C=new validation requirement + case updates. ANSWERED 2026-07-14 = A (0 = no limit, WAD, S2-R25). Applied: all 3 expecteds reworded to affirm 0 = no cap; flipped VIU-Verified; TICKET 4 DROPPED; FDBUG-9 closed accepted. Staged for TestRail push.</t>
         </is>
       </c>
     </row>
@@ -927,7 +947,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>FD-CALC-006 = VIU-Deviation (FDBUG-10 CONFIRMED AGAIN 2026-07-10: pct 0.005 accepted 201 and coerced to 0.01, resolved 0.02; flat 0.005 stored as 0.01). A=case-update to expect coercion + drop TICKET 5; B=dev change (store exact, likely new precision spec); C=file TICKET 5 as drafted.</t>
+          <t>FD-CALC-006 = VIU-Deviation (FDBUG-10 CONFIRMED AGAIN 2026-07-10: pct 0.005 accepted 201 and coerced to 0.01, resolved 0.02; flat 0.005 stored as 0.01). A=case-update to expect coercion + drop TICKET 5; B=dev change (store exact, likely new precision spec); C=file TICKET 5 as drafted. ANSWERED 2026-07-14 = A (rounding fine/expected). Applied: FD-CALC-006 expected reworded to expect the round-up-to-minimum coercion; flipped VIU-Verified; TICKET 5 DROPPED; FDBUG-10 closed accepted. Staged for TestRail push.</t>
         </is>
       </c>
     </row>
@@ -962,14 +982,14 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>FD-PROC-014 = VIU-Verified with a standing wording note (fresh pass 2026-07-10: pfee minimum silently STRIPPED on create - 201, no min field persisted). A=spec/data-model change + new cases for pfee minimums; B=case-update FD-PROC-014 to expect explicit reject/absent field vs today's silent strip (minor dev tweak or accepted-behavior wording).</t>
+          <t>FD-PROC-014 = VIU-Verified with a standing wording note (fresh pass 2026-07-10: pfee minimum silently STRIPPED on create - 201, no min field persisted). A=spec/data-model change + new cases for pfee minimums; B=case-update FD-PROC-014 to expect explicit reject/absent field vs today's silent strip (minor dev tweak or accepted-behavior wording). ANSWERED 2026-07-14 = B (don't support, make clear). Applied: FD-PROC-014 expected reworded to the explicit-reject + no-field behavior (matches the live 2026-07-13 finding: 400 'A processing fee cannot have a minimum or maximum cap.'; older silent-strip reading superseded); stays VIU-Verified. No dev ticket. Staged for TestRail push.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="75" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Notes: Round-2 questions raised after the FRESH FULL VIU PASS 2026-07-10 (FeesDiscounts_FreshVIU_2026-07-10.xlsx). TestRail IDs sourced from testrail-id-map.csv (standing rule 8). Round-1 (6 questions) was answered by Chris Ward 2026-07-09 - see PO-Questions-SIMPLE.md / spec-v1-reconciliation.md. Related unfiled Jira drafts: jira-bug-drafts.md TICKET 4 (maxCap 0) and TICKET 5 (tiny-percent rounding) - hold both until these rulings land. Bugs/defects stay OUT of the PO-facing tab (standing rule 7); these 4 items are genuine product decisions (which behavior is intended), not defect reports.</t>
+          <t>Notes: Round-2 questions raised after the FRESH FULL VIU PASS 2026-07-10 (FeesDiscounts_FreshVIU_2026-07-10.xlsx). TestRail IDs sourced from testrail-id-map.csv (standing rule 8). Round-1 (6 questions) was answered by Chris Ward 2026-07-09 - see PO-Questions-SIMPLE.md / spec-v1-reconciliation.md. ANSWERS RETURNED 2026-07-14 (Chris Ward): Q1=A, Q2=A, Q3=A, Q4=B - source chris-round2-answers-source.xlsx/.csv; action map applied to local artifacts (6 cases staged for TestRail push; jira drafts TICKET 4 (maxCap 0) + TICKET 5 (tiny-percent rounding) DROPPED as WAD/expected; no new tickets). Bugs/defects stay OUT of the PO-facing tab (standing rule 7); these 4 items were genuine product decisions (which behavior is intended), not defect reports.</t>
         </is>
       </c>
     </row>
